--- a/02_DIA_inicio_2026_analisis_assets/rbd_9419_liceo-municipal-enrique-backausse_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9419_liceo-municipal-enrique-backausse_nt2_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D13810A-30E4-4BDF-B03F-C989EC68D348}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2527EF78-2141-4644-BA1A-95910EE08C37}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C783219-2491-4DC5-B869-686C8C085641}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC49072C-7751-4CC5-9B59-D5AE313D5827}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D0A7A2E-CBC2-4D9F-9A10-D1EE11021DB0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B58B7D9-4815-4A9A-8250-C99B28E22FFA}"/>
 </file>